--- a/output/distribuidora_protocolo_entrega_parte_1.xlsx
+++ b/output/distribuidora_protocolo_entrega_parte_1.xlsx
@@ -1001,7 +1001,7 @@
       <c r="B7" s="17" t="n"/>
       <c r="C7" s="17" t="inlineStr">
         <is>
-          <t>LOLLA ITAIM</t>
+          <t>ZDELI ITAIM</t>
         </is>
       </c>
       <c r="D7" s="17" t="n"/>
@@ -1017,7 +1017,7 @@
       <c r="J7" s="17" t="n"/>
       <c r="K7" s="17" t="inlineStr">
         <is>
-          <t>SARJETA</t>
+          <t>ZDELI REBOUÇAS</t>
         </is>
       </c>
       <c r="L7" s="17" t="n"/>
@@ -1036,7 +1036,7 @@
       <c r="C8" s="3" t="n"/>
       <c r="D8" s="3" t="inlineStr">
         <is>
-          <t>03/06/2026</t>
+          <t>29/06/2026</t>
         </is>
       </c>
       <c r="E8" s="3" t="n"/>
@@ -1052,7 +1052,7 @@
       <c r="K8" s="3" t="n"/>
       <c r="L8" s="3" t="inlineStr">
         <is>
-          <t>03/06/2026</t>
+          <t>29/06/2026</t>
         </is>
       </c>
       <c r="M8" s="3" t="n"/>
@@ -1096,7 +1096,7 @@
       <c r="C10" s="17" t="n"/>
       <c r="D10" s="17" t="inlineStr">
         <is>
-          <t>42461</t>
+          <t>42607</t>
         </is>
       </c>
       <c r="E10" s="17" t="n"/>
@@ -1112,7 +1112,7 @@
       <c r="K10" s="17" t="n"/>
       <c r="L10" s="17" t="inlineStr">
         <is>
-          <t>42462</t>
+          <t>42608</t>
         </is>
       </c>
       <c r="M10" s="17" t="n"/>
@@ -1285,7 +1285,7 @@
       <c r="B20" s="17" t="n"/>
       <c r="C20" s="17" t="inlineStr">
         <is>
-          <t>GINGER PINHEIROS</t>
+          <t>ZDELI HADDOCK</t>
         </is>
       </c>
       <c r="D20" s="17" t="n"/>
@@ -1301,7 +1301,7 @@
       <c r="J20" s="17" t="n"/>
       <c r="K20" s="17" t="inlineStr">
         <is>
-          <t>CEPA BAR</t>
+          <t>ZDELI IAB - REPUBLICA</t>
         </is>
       </c>
       <c r="L20" s="17" t="n"/>
@@ -1320,7 +1320,7 @@
       <c r="C21" s="3" t="n"/>
       <c r="D21" s="3" t="inlineStr">
         <is>
-          <t>03/06/2026</t>
+          <t>29/06/2026</t>
         </is>
       </c>
       <c r="E21" s="3" t="n"/>
@@ -1336,7 +1336,7 @@
       <c r="K21" s="3" t="n"/>
       <c r="L21" s="3" t="inlineStr">
         <is>
-          <t>03/06/2026</t>
+          <t>29/06/2026</t>
         </is>
       </c>
       <c r="M21" s="3" t="n"/>
@@ -1380,7 +1380,7 @@
       <c r="C23" s="17" t="n"/>
       <c r="D23" s="17" t="inlineStr">
         <is>
-          <t>42463</t>
+          <t>42609</t>
         </is>
       </c>
       <c r="E23" s="17" t="n"/>
@@ -1396,7 +1396,7 @@
       <c r="K23" s="17" t="n"/>
       <c r="L23" s="17" t="inlineStr">
         <is>
-          <t>42464</t>
+          <t>42610</t>
         </is>
       </c>
       <c r="M23" s="17" t="n"/>
@@ -1569,7 +1569,7 @@
       <c r="B33" s="17" t="n"/>
       <c r="C33" s="17" t="inlineStr">
         <is>
-          <t>BBM (Adega Shopping)</t>
+          <t>SANTE BAR (ADEGA BAR)</t>
         </is>
       </c>
       <c r="D33" s="17" t="n"/>
@@ -1585,7 +1585,7 @@
       <c r="J33" s="17" t="n"/>
       <c r="K33" s="17" t="inlineStr">
         <is>
-          <t>A5HL (ADEGA A5HL)</t>
+          <t>TABERNA 474 (ADEGA LANCHE)</t>
         </is>
       </c>
       <c r="L33" s="17" t="n"/>
@@ -1604,7 +1604,7 @@
       <c r="C34" s="3" t="n"/>
       <c r="D34" s="3" t="inlineStr">
         <is>
-          <t>03/06/2026</t>
+          <t>29/06/2026</t>
         </is>
       </c>
       <c r="E34" s="3" t="n"/>
@@ -1620,7 +1620,7 @@
       <c r="K34" s="3" t="n"/>
       <c r="L34" s="3" t="inlineStr">
         <is>
-          <t>03/06/2026</t>
+          <t>29/06/2026</t>
         </is>
       </c>
       <c r="M34" s="3" t="n"/>
@@ -1664,7 +1664,7 @@
       <c r="C36" s="17" t="n"/>
       <c r="D36" s="17" t="inlineStr">
         <is>
-          <t>42465</t>
+          <t>42611</t>
         </is>
       </c>
       <c r="E36" s="17" t="n"/>
@@ -1680,7 +1680,7 @@
       <c r="K36" s="17" t="n"/>
       <c r="L36" s="17" t="inlineStr">
         <is>
-          <t>42466</t>
+          <t>42612</t>
         </is>
       </c>
       <c r="M36" s="17" t="n"/>
@@ -1869,7 +1869,7 @@
       <c r="J46" s="17" t="n"/>
       <c r="K46" s="17" t="inlineStr">
         <is>
-          <t>TABERNA 474 (ADEGA LANCHE)</t>
+          <t>A5HL (ADEGA A5HL)</t>
         </is>
       </c>
       <c r="L46" s="17" t="n"/>
@@ -1888,7 +1888,7 @@
       <c r="C47" s="3" t="n"/>
       <c r="D47" s="3" t="inlineStr">
         <is>
-          <t>03/06/2026</t>
+          <t>29/06/2026</t>
         </is>
       </c>
       <c r="E47" s="3" t="n"/>
@@ -1904,7 +1904,7 @@
       <c r="K47" s="3" t="n"/>
       <c r="L47" s="3" t="inlineStr">
         <is>
-          <t>03/06/2026</t>
+          <t>29/06/2026</t>
         </is>
       </c>
       <c r="M47" s="3" t="n"/>
@@ -1948,7 +1948,7 @@
       <c r="C49" s="17" t="n"/>
       <c r="D49" s="17" t="inlineStr">
         <is>
-          <t>42467</t>
+          <t>42613</t>
         </is>
       </c>
       <c r="E49" s="17" t="n"/>
@@ -1964,7 +1964,7 @@
       <c r="K49" s="17" t="n"/>
       <c r="L49" s="17" t="inlineStr">
         <is>
-          <t>42468</t>
+          <t>42614</t>
         </is>
       </c>
       <c r="M49" s="17" t="n"/>
@@ -2137,7 +2137,7 @@
       <c r="B59" s="17" t="n"/>
       <c r="C59" s="17" t="inlineStr">
         <is>
-          <t>SANTE BAR (ADEGA BAR)</t>
+          <t>JOBA BURGER POMPEIA LTDA</t>
         </is>
       </c>
       <c r="D59" s="17" t="n"/>
@@ -2153,7 +2153,7 @@
       <c r="J59" s="17" t="n"/>
       <c r="K59" s="17" t="inlineStr">
         <is>
-          <t>ZDELI ITAIM</t>
+          <t>CEPA BAR</t>
         </is>
       </c>
       <c r="L59" s="17" t="n"/>
@@ -2172,7 +2172,7 @@
       <c r="C60" s="3" t="n"/>
       <c r="D60" s="3" t="inlineStr">
         <is>
-          <t>03/06/2026</t>
+          <t>29/06/2026</t>
         </is>
       </c>
       <c r="E60" s="3" t="n"/>
@@ -2188,7 +2188,7 @@
       <c r="K60" s="3" t="n"/>
       <c r="L60" s="3" t="inlineStr">
         <is>
-          <t>03/06/2026</t>
+          <t>29/06/2026</t>
         </is>
       </c>
       <c r="M60" s="3" t="n"/>
@@ -2232,7 +2232,7 @@
       <c r="C62" s="17" t="n"/>
       <c r="D62" s="17" t="inlineStr">
         <is>
-          <t>42469</t>
+          <t>42615</t>
         </is>
       </c>
       <c r="E62" s="17" t="n"/>
@@ -2248,7 +2248,7 @@
       <c r="K62" s="17" t="n"/>
       <c r="L62" s="17" t="inlineStr">
         <is>
-          <t>42470</t>
+          <t>42616</t>
         </is>
       </c>
       <c r="M62" s="17" t="n"/>
